--- a/outputs/supplier_price_comparison.xlsx
+++ b/outputs/supplier_price_comparison.xlsx
@@ -880,7 +880,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>разница больше чем вдвое</t>
+          <t>крупная разница, сверить</t>
         </is>
       </c>
     </row>
